--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/TENNESSEE_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/TENNESSEE_2018.xlsx
@@ -715,7 +715,7 @@
         <v>11</v>
       </c>
       <c r="D20">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="21">
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="D21">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="22">
@@ -2479,7 +2479,7 @@
         <v>11</v>
       </c>
       <c r="D118">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="119">
@@ -3271,7 +3271,7 @@
         <v>11</v>
       </c>
       <c r="D162">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="163">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C172">
@@ -4531,7 +4531,7 @@
         <v>11</v>
       </c>
       <c r="D232">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="233">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C280">
@@ -5701,7 +5701,7 @@
         <v>101</v>
       </c>
       <c r="D297">
-        <v>0.009048557606163771</v>
+        <v>0.009048557606163772</v>
       </c>
     </row>
     <row r="298">
@@ -6421,7 +6421,7 @@
         <v>11</v>
       </c>
       <c r="D337">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="338">
@@ -7411,7 +7411,7 @@
         <v>11</v>
       </c>
       <c r="D392">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="393">
@@ -9805,7 +9805,7 @@
         <v>11</v>
       </c>
       <c r="D525">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="526">
@@ -10183,7 +10183,7 @@
         <v>11</v>
       </c>
       <c r="D546">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="547">
@@ -10237,7 +10237,7 @@
         <v>11</v>
       </c>
       <c r="D549">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="550">
@@ -10417,7 +10417,7 @@
         <v>11</v>
       </c>
       <c r="D559">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="560">
@@ -10525,7 +10525,7 @@
         <v>11</v>
       </c>
       <c r="D565">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="566">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C732">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C763">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C768">
@@ -17149,7 +17149,7 @@
         <v>11</v>
       </c>
       <c r="D933">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="934">
@@ -17329,7 +17329,7 @@
         <v>11</v>
       </c>
       <c r="D943">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="944">
@@ -17473,7 +17473,7 @@
         <v>11</v>
       </c>
       <c r="D951">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="952">
@@ -17905,7 +17905,7 @@
         <v>11</v>
       </c>
       <c r="D975">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="976">
@@ -18949,7 +18949,7 @@
         <v>11</v>
       </c>
       <c r="D1033">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="1034">
@@ -20677,7 +20677,7 @@
         <v>11</v>
       </c>
       <c r="D1129">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="1130">
@@ -20803,7 +20803,7 @@
         <v>11</v>
       </c>
       <c r="D1136">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="1137">
@@ -21235,7 +21235,7 @@
         <v>11</v>
       </c>
       <c r="D1160">
-        <v>0.0009854864719584303</v>
+        <v>0.0009854864719584305</v>
       </c>
     </row>
     <row r="1161">
